--- a/output/xlsx/matriz_diseno_20260811.xlsx
+++ b/output/xlsx/matriz_diseno_20260811.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado, incluyendo el estudiante que realizó la reserva, el ejemplar seleccionado y la fecha y hora de la operación.</t>
+          <t>El sistema deberá registrar la reserva asociándola al estudiante autenticado, incluyendo el ejemplar seleccionado y la fecha y hora de la operación.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Impedir reservas sobre ejemplares ya reservados</t>
+          <t>Impedir reserva de ejemplar con reserva activa</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mostrar confirmación de reserva</t>
+          <t>Mostrar confirmación de reserva registrada</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Actualizar información de préstamo</t>
+          <t>Actualizar información del préstamo</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
+          <t>El sistema deberá actualizar la información del préstamo después de registrar la devolución.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Registrar mascota</t>
+          <t>Registrar Libro</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
